--- a/mw-historic-data.xlsx
+++ b/mw-historic-data.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P201"/>
+  <dimension ref="A1:P202"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -10896,6 +10896,62 @@
         <v>0.97</v>
       </c>
     </row>
+    <row r="202">
+      <c r="A202" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>Q3</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>September</t>
+        </is>
+      </c>
+      <c r="D202" s="23" t="n">
+        <v>5040</v>
+      </c>
+      <c r="E202" s="24" t="n">
+        <v>5072302817</v>
+      </c>
+      <c r="F202" s="24" t="n">
+        <v>1006409</v>
+      </c>
+      <c r="G202" s="25">
+        <f>IFERROR(F202/F190-1,"")</f>
+        <v/>
+      </c>
+      <c r="H202" s="24" t="n">
+        <v>860000</v>
+      </c>
+      <c r="I202" s="23" t="n">
+        <v>16500</v>
+      </c>
+      <c r="J202" s="23" t="n">
+        <v>26131</v>
+      </c>
+      <c r="K202" s="25" t="n">
+        <v>0.3779999999999999</v>
+      </c>
+      <c r="L202" s="26">
+        <f>J202/D202</f>
+        <v/>
+      </c>
+      <c r="M202" s="26" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="N202" s="27" t="n">
+        <v>34</v>
+      </c>
+      <c r="O202" s="27" t="n">
+        <v>51</v>
+      </c>
+      <c r="P202" s="25" t="n">
+        <v>0.98</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:P1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -10909,7 +10965,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P201"/>
+  <dimension ref="A1:P202"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -21375,6 +21431,62 @@
         <v>0.97</v>
       </c>
     </row>
+    <row r="202">
+      <c r="A202" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>Q3</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>September</t>
+        </is>
+      </c>
+      <c r="D202" s="23" t="n">
+        <v>893</v>
+      </c>
+      <c r="E202" s="24" t="n">
+        <v>1015028255</v>
+      </c>
+      <c r="F202" s="24" t="n">
+        <v>1136650</v>
+      </c>
+      <c r="G202" s="25">
+        <f>IFERROR(F202/F190-1,"")</f>
+        <v/>
+      </c>
+      <c r="H202" s="24" t="n">
+        <v>1043000</v>
+      </c>
+      <c r="I202" s="23" t="n">
+        <v>3106</v>
+      </c>
+      <c r="J202" s="23" t="n">
+        <v>5168</v>
+      </c>
+      <c r="K202" s="25" t="n">
+        <v>0.358</v>
+      </c>
+      <c r="L202" s="26">
+        <f>J202/D202</f>
+        <v/>
+      </c>
+      <c r="M202" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="N202" s="27" t="n">
+        <v>38</v>
+      </c>
+      <c r="O202" s="27" t="n">
+        <v>56</v>
+      </c>
+      <c r="P202" s="25" t="n">
+        <v>0.97</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:P1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -21388,7 +21500,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P201"/>
+  <dimension ref="A1:P202"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -31854,6 +31966,62 @@
         <v>0.97</v>
       </c>
     </row>
+    <row r="202">
+      <c r="A202" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>Q3</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>September</t>
+        </is>
+      </c>
+      <c r="D202" s="23" t="n">
+        <v>1937</v>
+      </c>
+      <c r="E202" s="24" t="n">
+        <v>2003478196</v>
+      </c>
+      <c r="F202" s="24" t="n">
+        <v>1034320</v>
+      </c>
+      <c r="G202" s="25">
+        <f>IFERROR(F202/F190-1,"")</f>
+        <v/>
+      </c>
+      <c r="H202" s="24" t="n">
+        <v>810000</v>
+      </c>
+      <c r="I202" s="23" t="n">
+        <v>6521</v>
+      </c>
+      <c r="J202" s="23" t="n">
+        <v>9865</v>
+      </c>
+      <c r="K202" s="25" t="n">
+        <v>0.385</v>
+      </c>
+      <c r="L202" s="26">
+        <f>J202/D202</f>
+        <v/>
+      </c>
+      <c r="M202" s="26" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="N202" s="27" t="n">
+        <v>33</v>
+      </c>
+      <c r="O202" s="27" t="n">
+        <v>45</v>
+      </c>
+      <c r="P202" s="25" t="n">
+        <v>0.99</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:P1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -31867,7 +32035,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P201"/>
+  <dimension ref="A1:P202"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -42333,6 +42501,62 @@
         <v>0.97</v>
       </c>
     </row>
+    <row r="202">
+      <c r="A202" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>Q3</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>September</t>
+        </is>
+      </c>
+      <c r="D202" s="23" t="n">
+        <v>187</v>
+      </c>
+      <c r="E202" s="24" t="n">
+        <v>151554688</v>
+      </c>
+      <c r="F202" s="24" t="n">
+        <v>810453</v>
+      </c>
+      <c r="G202" s="25">
+        <f>IFERROR(F202/F190-1,"")</f>
+        <v/>
+      </c>
+      <c r="H202" s="24" t="n">
+        <v>762500</v>
+      </c>
+      <c r="I202" s="23" t="n">
+        <v>566</v>
+      </c>
+      <c r="J202" s="23" t="n">
+        <v>1080</v>
+      </c>
+      <c r="K202" s="25" t="n">
+        <v>0.338</v>
+      </c>
+      <c r="L202" s="26">
+        <f>J202/D202</f>
+        <v/>
+      </c>
+      <c r="M202" s="26" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="N202" s="27" t="n">
+        <v>44</v>
+      </c>
+      <c r="O202" s="27" t="n">
+        <v>63</v>
+      </c>
+      <c r="P202" s="25" t="n">
+        <v>0.97</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:P1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -42346,7 +42570,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P201"/>
+  <dimension ref="A1:P202"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -52812,6 +53036,62 @@
         <v>0.97</v>
       </c>
     </row>
+    <row r="202">
+      <c r="A202" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>Q3</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>September</t>
+        </is>
+      </c>
+      <c r="D202" s="23" t="n">
+        <v>936</v>
+      </c>
+      <c r="E202" s="24" t="n">
+        <v>848688834</v>
+      </c>
+      <c r="F202" s="24" t="n">
+        <v>906719</v>
+      </c>
+      <c r="G202" s="25">
+        <f>IFERROR(F202/F190-1,"")</f>
+        <v/>
+      </c>
+      <c r="H202" s="24" t="n">
+        <v>855000</v>
+      </c>
+      <c r="I202" s="23" t="n">
+        <v>2661</v>
+      </c>
+      <c r="J202" s="23" t="n">
+        <v>4631</v>
+      </c>
+      <c r="K202" s="25" t="n">
+        <v>0.356</v>
+      </c>
+      <c r="L202" s="26">
+        <f>J202/D202</f>
+        <v/>
+      </c>
+      <c r="M202" s="26" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="N202" s="27" t="n">
+        <v>35</v>
+      </c>
+      <c r="O202" s="27" t="n">
+        <v>55</v>
+      </c>
+      <c r="P202" s="25" t="n">
+        <v>0.97</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:P1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -52825,7 +53105,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P201"/>
+  <dimension ref="A1:P202"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -63291,6 +63571,62 @@
         <v>0.96</v>
       </c>
     </row>
+    <row r="202">
+      <c r="A202" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>Q3</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>September</t>
+        </is>
+      </c>
+      <c r="D202" s="23" t="n">
+        <v>502</v>
+      </c>
+      <c r="E202" s="24" t="n">
+        <v>571790533</v>
+      </c>
+      <c r="F202" s="24" t="n">
+        <v>1139025</v>
+      </c>
+      <c r="G202" s="25">
+        <f>IFERROR(F202/F190-1,"")</f>
+        <v/>
+      </c>
+      <c r="H202" s="24" t="n">
+        <v>982500</v>
+      </c>
+      <c r="I202" s="23" t="n">
+        <v>1733</v>
+      </c>
+      <c r="J202" s="23" t="n">
+        <v>2625</v>
+      </c>
+      <c r="K202" s="25" t="n">
+        <v>0.404</v>
+      </c>
+      <c r="L202" s="26">
+        <f>J202/D202</f>
+        <v/>
+      </c>
+      <c r="M202" s="26" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="N202" s="27" t="n">
+        <v>33</v>
+      </c>
+      <c r="O202" s="27" t="n">
+        <v>53</v>
+      </c>
+      <c r="P202" s="25" t="n">
+        <v>0.96</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:P1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -63304,7 +63640,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P201"/>
+  <dimension ref="A1:P202"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -73770,6 +74106,62 @@
         <v>0.98</v>
       </c>
     </row>
+    <row r="202">
+      <c r="A202" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>Q3</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>September</t>
+        </is>
+      </c>
+      <c r="D202" s="23" t="n">
+        <v>552</v>
+      </c>
+      <c r="E202" s="24" t="n">
+        <v>457133675</v>
+      </c>
+      <c r="F202" s="24" t="n">
+        <v>828141</v>
+      </c>
+      <c r="G202" s="25">
+        <f>IFERROR(F202/F190-1,"")</f>
+        <v/>
+      </c>
+      <c r="H202" s="24" t="n">
+        <v>770000</v>
+      </c>
+      <c r="I202" s="23" t="n">
+        <v>1834</v>
+      </c>
+      <c r="J202" s="23" t="n">
+        <v>2622</v>
+      </c>
+      <c r="K202" s="25" t="n">
+        <v>0.411</v>
+      </c>
+      <c r="L202" s="26">
+        <f>J202/D202</f>
+        <v/>
+      </c>
+      <c r="M202" s="26" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="N202" s="27" t="n">
+        <v>30</v>
+      </c>
+      <c r="O202" s="27" t="n">
+        <v>48</v>
+      </c>
+      <c r="P202" s="25" t="n">
+        <v>0.98</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:P1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -73783,7 +74175,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P201"/>
+  <dimension ref="A1:P202"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -84249,6 +84641,62 @@
         <v>0.97</v>
       </c>
     </row>
+    <row r="202">
+      <c r="A202" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>Q3</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>September</t>
+        </is>
+      </c>
+      <c r="D202" s="23" t="n">
+        <v>33</v>
+      </c>
+      <c r="E202" s="24" t="n">
+        <v>24628636</v>
+      </c>
+      <c r="F202" s="24" t="n">
+        <v>746322</v>
+      </c>
+      <c r="G202" s="25">
+        <f>IFERROR(F202/F190-1,"")</f>
+        <v/>
+      </c>
+      <c r="H202" s="24" t="n">
+        <v>740000</v>
+      </c>
+      <c r="I202" s="23" t="n">
+        <v>79</v>
+      </c>
+      <c r="J202" s="23" t="n">
+        <v>140</v>
+      </c>
+      <c r="K202" s="25" t="n">
+        <v>0.406</v>
+      </c>
+      <c r="L202" s="26">
+        <f>J202/D202</f>
+        <v/>
+      </c>
+      <c r="M202" s="26" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="N202" s="27" t="n">
+        <v>29</v>
+      </c>
+      <c r="O202" s="27" t="n">
+        <v>51</v>
+      </c>
+      <c r="P202" s="25" t="n">
+        <v>0.97</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:P1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
